--- a/backend/assets/nakladnoy/warehouse/602-wh-6.0.2.xlsx
+++ b/backend/assets/nakladnoy/warehouse/602-wh-6.0.2.xlsx
@@ -7607,6 +7607,6 @@
     <mergeCell ref="S217:U217"/>
   </mergeCells>
   <pageMargins left="0.42" right="0" top="0.2" bottom="0.2" header="0" footer="0"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
 </file>